--- a/data/2026/cjsl/fall/brooklyn-united-academy-b2013-2014-park-slope-select.xlsx
+++ b/data/2026/cjsl/fall/brooklyn-united-academy-b2013-2014-park-slope-select.xlsx
@@ -214,7 +214,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>
@@ -449,12 +449,12 @@
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Saturday, November 14, 2026</t>
+          <t>Sunday, November 15, 2026</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>16:30 EST</t>
+          <t>12:30 EST</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>Hamilton Metz Field - Field 1</t>
+          <t>Bush Terminal Piers Park - Soccer 03 (Back field)</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/brooklyn-united-academy-b2013-2014-park-slope-select.xlsx
+++ b/data/2026/cjsl/fall/brooklyn-united-academy-b2013-2014-park-slope-select.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6 - 0</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/brooklyn-united-academy-b2013-2014-park-slope-select.xlsx
+++ b/data/2026/cjsl/fall/brooklyn-united-academy-b2013-2014-park-slope-select.xlsx
@@ -175,36 +175,36 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Saturday, September 26, 2026</t>
+          <t>Saturday, October  3, 2026</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>10:35 EDT</t>
+          <t>16:30 EDT</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>NY Kids S.C. 2013/2014 boys</t>
+          <t>Brooklyn United Academy B2013/2014 Park Slope Select</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6 - 0</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>Brooklyn United Academy B2013/2014 Park Slope Select</t>
+          <t>Metropolitan Oval Academy Brooklyn 2013/14 Boys U13 Gray</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>Grover Cleveland Playground - Grover Cleveland Playground: Soccer-01</t>
+          <t>Hamilton Metz Field - Field 1</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -214,42 +214,42 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>Rained Out</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October  3, 2026</t>
+          <t>Sunday, October 18, 2026</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>16:30 EDT</t>
+          <t>17:00 EDT</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>Brooklyn United Academy B2013/2014 Park Slope Select</t>
+          <t>Dynamo Soccer Club 2014</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>6 - 0</t>
+          <t>1 - 3</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>Metropolitan Oval Academy Brooklyn 2013/14 Boys U13 Gray</t>
+          <t>Brooklyn United Academy B2013/2014 Park Slope Select</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>Hamilton Metz Field - Field 1</t>
+          <t>KAISER PARK - KAISER PARK</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -265,21 +265,21 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Sunday, October 18, 2026</t>
+          <t>Saturday, October 24, 2026</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>17:00 EDT</t>
+          <t>17:30 EDT</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>Dynamo Soccer Club 2014</t>
+          <t>South Brooklyn FC #2 2013/2014</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -294,7 +294,7 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>KAISER PARK - KAISER PARK</t>
+          <t>Calvert Vaux/Verrazano Complex - Field #1</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -310,21 +310,21 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 24, 2026</t>
+          <t>Saturday, October 31, 2026</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>17:30 EDT</t>
+          <t>16:30 EDT</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>South Brooklyn FC #2 2013/2014</t>
+          <t>Brooklyn United Academy B2013/2014 Park Slope Select</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -334,12 +334,12 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>Brooklyn United Academy B2013/2014 Park Slope Select</t>
+          <t>NY Kids S.C. 2013/2014 boys</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>Calvert Vaux/Verrazano Complex - Field #1</t>
+          <t>Hamilton Metz Field - Field 1</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -355,21 +355,21 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 31, 2026</t>
+          <t>Saturday, November  7, 2026</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>16:30 EDT</t>
+          <t>10:35 EST</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>Brooklyn United Academy B2013/2014 Park Slope Select</t>
+          <t>Metropolitan Oval Academy Brooklyn 2013/14 Boys U13 Gray</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -379,12 +379,12 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>NY Kids S.C. 2013/2014 boys</t>
+          <t>Brooklyn United Academy B2013/2014 Park Slope Select</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>Hamilton Metz Field - Field 1</t>
+          <t>Red Hook Field #5 - Field 5 11v11</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -400,21 +400,21 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Saturday, November  7, 2026</t>
+          <t>Sunday, November 15, 2026</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>10:35 EST</t>
+          <t>12:30 EST</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>Metropolitan Oval Academy Brooklyn 2013/14 Boys U13 Gray</t>
+          <t>Brooklyn United Academy B2013/2014 Park Slope Select</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -424,12 +424,12 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>Brooklyn United Academy B2013/2014 Park Slope Select</t>
+          <t>Dynamo Soccer Club 2014</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>Red Hook Field #5 - Field 5 11v11</t>
+          <t>Bush Terminal Piers Park - Soccer 03 (Back field)</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -439,27 +439,27 @@
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Sunday, November 15, 2026</t>
+          <t>Saturday, November 21, 2026</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>12:30 EST</t>
+          <t>08:15 EST</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>Brooklyn United Academy B2013/2014 Park Slope Select</t>
+          <t>NY Kids S.C. 2013/2014 boys</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -469,12 +469,12 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>Dynamo Soccer Club 2014</t>
+          <t>Brooklyn United Academy B2013/2014 Park Slope Select</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>Bush Terminal Piers Park - Soccer 03 (Back field)</t>
+          <t>Grover Cleveland Playground - Grover Cleveland Playground: Soccer-01</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/brooklyn-united-academy-b2013-2014-park-slope-select.xlsx
+++ b/data/2026/cjsl/fall/brooklyn-united-academy-b2013-2014-park-slope-select.xlsx
@@ -284,7 +284,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4 - 1</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
